--- a/src/Tests/OnlineRegistry/data/attendance.xlsx
+++ b/src/Tests/OnlineRegistry/data/attendance.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\coding\ScheduleLib\src\Tests\OnlineRegistry\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CC26A83-C534-4836-AA3E-36F92AAA230F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B8CA346-3EEC-4EAA-952E-4E2C8919A015}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1500" yWindow="1956" windowWidth="17280" windowHeight="9072" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="348" windowWidth="23256" windowHeight="12720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="C++ (curs)" sheetId="1" r:id="rId1"/>
@@ -67,7 +67,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -75,13 +75,32 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -96,8 +115,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -478,6 +499,9 @@
       <c r="A2" t="s">
         <v>10</v>
       </c>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
@@ -503,6 +527,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -533,23 +558,23 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>1</v>
       </c>
-      <c r="C3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="C3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>1</v>
       </c>
     </row>
